--- a/excel-expense-tracker-mini-project.xlxs.xlsx
+++ b/excel-expense-tracker-mini-project.xlxs.xlsx
@@ -2,21 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="17175" windowHeight="8460"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="17175" windowHeight="8460" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="pivot_Analysis" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <pivotCaches>
+    <pivotCache cacheId="6" r:id="rId4"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="23">
   <si>
     <t>Date</t>
   </si>
@@ -73,6 +76,18 @@
   </si>
   <si>
     <t>Dinner</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
   </si>
 </sst>
 </file>
@@ -116,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +142,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -134,6 +157,723 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:pivotSource>
+    <c:name>[excel-expense-tracker-mini-project.xlxs.xlsx]pivot_Analysis!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+    </c:title>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>pivot_Analysis!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>pivot_Analysis!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Entertainment</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Food</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Groceries</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Transport</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Utilities</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>pivot_Analysis!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:pivotSource>
+    <c:name>[excel-expense-tracker-mini-project.xlxs.xlsx]pivot_Analysis!PivotTable3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+    </c:title>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>pivot_Analysis!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>pivot_Analysis!$A$13:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Card</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cash</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>UPI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>pivot_Analysis!$B$13:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>589</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="89625344"/>
+        <c:axId val="89626880"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="89625344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="89626880"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="89626880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="89625344"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:pivotSource>
+    <c:name>[excel-expense-tracker-mini-project.xlxs.xlsx]pivot_Analysis!PivotTable5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+    </c:title>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>pivot_Analysis!$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>pivot_Analysis!$A$19:$A$24</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>01/01/26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>02/01/26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>03/01/26</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>04/01/26</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>05/01/26</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>pivot_Analysis!$B$19:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>220</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="76380032"/>
+        <c:axId val="76381568"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="76380032"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="76381568"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="76381568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="76380032"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>257174</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="admin" refreshedDate="46028.865324074075" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="6">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E7" sheet="Dataset"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-05-02T00:00:00" count="5">
+        <d v="2026-01-01T00:00:00"/>
+        <d v="2026-02-01T00:00:00"/>
+        <d v="2026-03-01T00:00:00"/>
+        <d v="2026-04-01T00:00:00"/>
+        <d v="2026-05-01T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Food"/>
+        <s v="Transport"/>
+        <s v="Groceries"/>
+        <s v="Entertainment"/>
+        <s v="Utilities"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Description" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Payment Mode" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Cash"/>
+        <s v="UPI"/>
+        <s v="Card"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="520"/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="6">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Lunch"/>
+    <x v="0"/>
+    <n v="150"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Bus fare"/>
+    <x v="1"/>
+    <n v="40"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Vegetables"/>
+    <x v="2"/>
+    <n v="520"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Movie"/>
+    <x v="1"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Mobile Recharge"/>
+    <x v="1"/>
+    <n v="249"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <s v="Dinner"/>
+    <x v="0"/>
+    <n v="220"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A18:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,10 +1161,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="30">
+    <row r="1" spans="1:8" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,7 +1181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>46023</v>
       </c>
@@ -458,7 +1198,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:8" ht="30">
       <c r="A3" s="2">
         <v>46023</v>
       </c>
@@ -475,7 +1215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30">
+    <row r="4" spans="1:8" ht="30">
       <c r="A4" s="2">
         <v>46054</v>
       </c>
@@ -492,7 +1232,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:8" ht="30">
       <c r="A5" s="2">
         <v>46082</v>
       </c>
@@ -509,7 +1249,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:8" ht="30">
       <c r="A6" s="2">
         <v>46113</v>
       </c>
@@ -526,7 +1266,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>46143</v>
       </c>
@@ -541,6 +1281,11 @@
       </c>
       <c r="E7" s="3">
         <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="H12" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -550,18 +1295,324 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30">
+      <c r="A3" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30">
+      <c r="A4" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30">
+      <c r="A5" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30">
+      <c r="A6" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9">
+        <f>SUMIF(B2:B7,"FOOD",E2:E7)</f>
+        <v>370</v>
+      </c>
+      <c r="E9">
+        <f>SUM(E2:E7)</f>
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="E10">
+        <f>COUNT(E2:E7)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="E11">
+        <f>AVERAGE(E2:E7)</f>
+        <v>246.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="E12">
+        <f>MAX(E2:E7)</f>
+        <v>520</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A3:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="6">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="6">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="7">
+        <v>46023</v>
+      </c>
+      <c r="B19" s="6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="7">
+        <v>46054</v>
+      </c>
+      <c r="B20" s="6">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="7">
+        <v>46082</v>
+      </c>
+      <c r="B21" s="6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B22" s="6">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="7">
+        <v>46143</v>
+      </c>
+      <c r="B23" s="6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1479</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>